--- a/src/test/resources/testdata/searchCustomerProfile.xlsx
+++ b/src/test/resources/testdata/searchCustomerProfile.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Downloads\management\selenium demo\src\test\resources\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Documents\MicroscanAutomation\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE86B595-F68D-4F22-8417-F0D1A3112FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C8EB75-96C9-4775-A95E-E9B6D6209CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{21B7F7A0-8745-4C8D-A4CA-8A5DBDE2F556}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{21B7F7A0-8745-4C8D-A4CA-8A5DBDE2F556}"/>
   </bookViews>
   <sheets>
     <sheet name="CustomerDetails" sheetId="5" r:id="rId1"/>
